--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_320_R32.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_320_R32.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.7155</v>
+        <v>5.329</v>
       </c>
       <c r="E2" t="n">
-        <v>4.6258</v>
+        <v>5.6008</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.9103</v>
+        <v>-0.2718</v>
       </c>
       <c r="G2" t="n">
         <v>3.4595</v>
@@ -610,13 +610,13 @@
         <v>1.3917</v>
       </c>
       <c r="S2" t="n">
-        <v>-2.6564</v>
+        <v>-1.0429</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.1123</v>
+        <v>-0.1373</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.5441</v>
+        <v>-0.9056</v>
       </c>
       <c r="V2" t="n">
         <v>2.6805</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.312</v>
+        <v>2.6665</v>
       </c>
       <c r="E3" t="n">
-        <v>1.332</v>
+        <v>1.9217</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9801</v>
+        <v>0.7448</v>
       </c>
       <c r="G3" t="n">
         <v>3.9134</v>
@@ -688,13 +688,13 @@
         <v>1.3917</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.2972</v>
+        <v>-0.9427</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6642</v>
+        <v>-0.0745</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.633</v>
+        <v>-0.8683</v>
       </c>
       <c r="V3" t="n">
         <v>-0.5361</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. GIEDRAITIS</t>
+          <t>A. BUTKEVICIUS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7932</v>
+        <v>2.1826</v>
       </c>
       <c r="E4" t="n">
-        <v>2.1299</v>
+        <v>0.1655</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3368</v>
+        <v>2.017</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9162</v>
+        <v>3.5787</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4778</v>
+        <v>2.9028</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4384</v>
+        <v>0.6758999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9307</v>
+        <v>2.3064</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8571</v>
+        <v>1.7309</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0736</v>
+        <v>0.5754</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.0144</v>
+        <v>1.2724</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3792</v>
+        <v>1.1719</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3648</v>
+        <v>0.1005</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6959</v>
+        <v>-0.232</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R4" t="n">
-        <v>0.6959</v>
+        <v>0.9278</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3229</v>
+        <v>-0.3756</v>
       </c>
       <c r="T4" t="n">
-        <v>1.1993</v>
+        <v>-0.1924</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.8764</v>
+        <v>-0.1832</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.1418</v>
+        <v>-0.7886</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>-0.7886</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. BUTKEVICIUS</t>
+          <t>N. WILLIAMS-GOSS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5689</v>
+        <v>1.3464</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.3809</v>
+        <v>2.4002</v>
       </c>
       <c r="F5" t="n">
-        <v>1.9498</v>
+        <v>-1.0538</v>
       </c>
       <c r="G5" t="n">
-        <v>3.5787</v>
+        <v>1.2598</v>
       </c>
       <c r="H5" t="n">
-        <v>2.9028</v>
+        <v>-0.5872000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6758999999999999</v>
+        <v>1.847</v>
       </c>
       <c r="J5" t="n">
-        <v>2.3064</v>
+        <v>2.1965</v>
       </c>
       <c r="K5" t="n">
-        <v>1.7309</v>
+        <v>-0.5504</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5754</v>
+        <v>2.7469</v>
       </c>
       <c r="M5" t="n">
-        <v>1.2724</v>
+        <v>-0.9367</v>
       </c>
       <c r="N5" t="n">
-        <v>1.1719</v>
+        <v>-0.0368</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1005</v>
+        <v>-0.8999</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.232</v>
+        <v>0.6959</v>
       </c>
       <c r="Q5" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9278</v>
+        <v>1.8556</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.9893</v>
+        <v>-1.0036</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7389</v>
+        <v>0.2912</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2504</v>
+        <v>-1.2948</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.7886</v>
+        <v>0.3943</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.7886</v>
+        <v>1.0722</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. TUBELIS</t>
+          <t>D. GIEDRAITIS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9506</v>
+        <v>1.3042</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5671</v>
+        <v>1.5402</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3835</v>
+        <v>-0.236</v>
       </c>
       <c r="G6" t="n">
-        <v>1.2592</v>
+        <v>0.9162</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8174</v>
+        <v>0.4778</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4418</v>
+        <v>0.4384</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4802</v>
+        <v>0.9307</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2961</v>
+        <v>0.8571</v>
       </c>
       <c r="L6" t="n">
-        <v>0.184</v>
+        <v>0.0736</v>
       </c>
       <c r="M6" t="n">
-        <v>0.779</v>
+        <v>-0.0144</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5213</v>
+        <v>-0.3792</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2578</v>
+        <v>0.3648</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.6237</v>
+        <v>0.6959</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0.6959</v>
       </c>
       <c r="S6" t="n">
-        <v>2.529</v>
+        <v>-0.1661</v>
       </c>
       <c r="T6" t="n">
-        <v>2.4065</v>
+        <v>0.6095</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1226</v>
+        <v>-0.7756</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.214</v>
+        <v>-0.1418</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.214</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0418</v>
+        <v>0.2858</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7191</v>
+        <v>-0.1726</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7609</v>
+        <v>0.4585</v>
       </c>
       <c r="G7" t="n">
         <v>1.3166</v>
@@ -1000,13 +1000,13 @@
         <v>1.1598</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2227</v>
+        <v>0.4668</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5975</v>
+        <v>-0.051</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8202</v>
+        <v>0.5177</v>
       </c>
       <c r="V7" t="n">
         <v>-1.4975</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>N. WILLIAMS-GOSS</t>
+          <t>A. TUBELIS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2775</v>
+        <v>-1.1569</v>
       </c>
       <c r="E8" t="n">
-        <v>1.146</v>
+        <v>-1.1707</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.4235</v>
+        <v>0.0138</v>
       </c>
       <c r="G8" t="n">
-        <v>1.2598</v>
+        <v>1.2592</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5872000000000001</v>
+        <v>0.8174</v>
       </c>
       <c r="I8" t="n">
-        <v>1.847</v>
+        <v>0.4418</v>
       </c>
       <c r="J8" t="n">
-        <v>2.1965</v>
+        <v>0.4802</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.5504</v>
+        <v>0.2961</v>
       </c>
       <c r="L8" t="n">
-        <v>2.7469</v>
+        <v>0.184</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.9367</v>
+        <v>0.779</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0368</v>
+        <v>0.5213</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.8999</v>
+        <v>0.2578</v>
       </c>
       <c r="P8" t="n">
+        <v>-1.6237</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>-2.3195</v>
+      </c>
+      <c r="R8" t="n">
         <v>0.6959</v>
       </c>
-      <c r="Q8" t="n">
-        <v>-1.1598</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.8556</v>
-      </c>
       <c r="S8" t="n">
-        <v>-2.6274</v>
+        <v>0.4215</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.963</v>
+        <v>0.6686</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.6645</v>
+        <v>-0.2471</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3943</v>
+        <v>-1.214</v>
       </c>
       <c r="W8" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>L. BIRUTIS</t>
+          <t>E. ULANOVAS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,40 +1111,40 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3373</v>
+        <v>-1.564</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6959</v>
+        <v>-0.2802</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.0332</v>
+        <v>-1.2838</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.1214</v>
+        <v>-2.0918</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.4924</v>
+        <v>-1.9747</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.629</v>
+        <v>-0.1171</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6586</v>
+        <v>-0.4691</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5482</v>
+        <v>-0.9341</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1104</v>
+        <v>0.465</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.78</v>
+        <v>-1.6227</v>
       </c>
       <c r="N9" t="n">
         <v>-1.0406</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.7393999999999999</v>
+        <v>-0.5821</v>
       </c>
       <c r="P9" t="n">
         <v>0.6959</v>
@@ -1156,28 +1156,28 @@
         <v>0.6959</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4129</v>
+        <v>-0.168</v>
       </c>
       <c r="T9" t="n">
-        <v>0.8259</v>
+        <v>0.1889</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4129</v>
+        <v>-0.3569</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.3247</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.7886</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E. ULANOVAS</t>
+          <t>L. BIRUTIS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,40 +1189,40 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.6723</v>
+        <v>-1.8524</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.3549</v>
+        <v>0.1808</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.3174</v>
+        <v>-2.0332</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.0918</v>
+        <v>-1.1214</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.9747</v>
+        <v>-0.4924</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1171</v>
+        <v>-0.629</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.4691</v>
+        <v>0.6586</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.9341</v>
+        <v>0.5482</v>
       </c>
       <c r="L10" t="n">
-        <v>0.465</v>
+        <v>0.1104</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.6227</v>
+        <v>-1.78</v>
       </c>
       <c r="N10" t="n">
         <v>-1.0406</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.5821</v>
+        <v>-0.7393999999999999</v>
       </c>
       <c r="P10" t="n">
         <v>0.6959</v>
@@ -1234,22 +1234,22 @@
         <v>0.6959</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2763</v>
+        <v>-0.1021</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1142</v>
+        <v>0.3108</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3905</v>
+        <v>-0.4129</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-1.3247</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-0.7886</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.8424</v>
+        <v>-4.542</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.6419</v>
+        <v>-4.039</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2005</v>
+        <v>-0.5029</v>
       </c>
       <c r="G11" t="n">
         <v>-3.6249</v>
@@ -1312,13 +1312,13 @@
         <v>0.9278</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0145</v>
+        <v>-0.6851</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3778</v>
+        <v>-0.0193</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3633</v>
+        <v>-0.6657</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,28 +1345,28 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.252499999999999</v>
+        <v>3.9992</v>
       </c>
       <c r="E12" t="n">
-        <v>5.399899999999999</v>
+        <v>6.146699999999999</v>
       </c>
       <c r="F12" t="n">
         <v>-2.1474</v>
       </c>
       <c r="G12" t="n">
-        <v>8.865299999999998</v>
+        <v>8.8653</v>
       </c>
       <c r="H12" t="n">
         <v>2.5747</v>
       </c>
       <c r="I12" t="n">
-        <v>6.2906</v>
+        <v>6.290600000000001</v>
       </c>
       <c r="J12" t="n">
         <v>10.0464</v>
       </c>
       <c r="K12" t="n">
-        <v>2.920300000000001</v>
+        <v>2.9203</v>
       </c>
       <c r="L12" t="n">
         <v>7.125900000000001</v>
@@ -1375,7 +1375,7 @@
         <v>-1.181</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.3454999999999999</v>
+        <v>-0.3455000000000001</v>
       </c>
       <c r="O12" t="n">
         <v>-0.8352999999999998</v>
@@ -1390,13 +1390,13 @@
         <v>10.438</v>
       </c>
       <c r="S12" t="n">
-        <v>-4.344599999999999</v>
+        <v>-3.5978</v>
       </c>
       <c r="T12" t="n">
-        <v>0.8477999999999997</v>
+        <v>1.5945</v>
       </c>
       <c r="U12" t="n">
-        <v>-5.1923</v>
+        <v>-5.192399999999999</v>
       </c>
       <c r="V12" t="n">
         <v>-2.4279</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>W. TAVARES</t>
+          <t>C. OKEKE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,64 +1423,64 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.9674</v>
+        <v>4.3496</v>
       </c>
       <c r="E13" t="n">
-        <v>4.3952</v>
+        <v>3.8471</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5722</v>
+        <v>0.5024999999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8703</v>
+        <v>2.2606</v>
       </c>
       <c r="H13" t="n">
-        <v>1.3219</v>
+        <v>2.4814</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.4516</v>
+        <v>-0.2208</v>
       </c>
       <c r="J13" t="n">
-        <v>1.3639</v>
+        <v>2.4144</v>
       </c>
       <c r="K13" t="n">
-        <v>1.1798</v>
+        <v>1.9494</v>
       </c>
       <c r="L13" t="n">
-        <v>0.184</v>
+        <v>0.465</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.4936</v>
+        <v>-0.1538</v>
       </c>
       <c r="N13" t="n">
-        <v>0.142</v>
+        <v>0.5321</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.6356000000000001</v>
+        <v>-0.6859</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.3195</v>
+        <v>0.9278</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.4793</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.1598</v>
+        <v>0.9278</v>
       </c>
       <c r="S13" t="n">
-        <v>3.5943</v>
+        <v>0.6251</v>
       </c>
       <c r="T13" t="n">
-        <v>3.6883</v>
+        <v>0.8966</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.094</v>
+        <v>-0.2715</v>
       </c>
       <c r="V13" t="n">
-        <v>2.8223</v>
+        <v>0.5361</v>
       </c>
       <c r="W13" t="n">
-        <v>2.8223</v>
+        <v>0.5361</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C. OKEKE</t>
+          <t>W. TAVARES</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.2938</v>
+        <v>2.7492</v>
       </c>
       <c r="E14" t="n">
-        <v>4.083</v>
+        <v>2.1541</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2108</v>
+        <v>0.595</v>
       </c>
       <c r="G14" t="n">
-        <v>2.2606</v>
+        <v>0.8703</v>
       </c>
       <c r="H14" t="n">
-        <v>2.4814</v>
+        <v>1.3219</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2208</v>
+        <v>-0.4516</v>
       </c>
       <c r="J14" t="n">
-        <v>2.4144</v>
+        <v>1.3639</v>
       </c>
       <c r="K14" t="n">
-        <v>1.9494</v>
+        <v>1.1798</v>
       </c>
       <c r="L14" t="n">
-        <v>0.465</v>
+        <v>0.184</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.1538</v>
+        <v>-0.4936</v>
       </c>
       <c r="N14" t="n">
-        <v>0.5321</v>
+        <v>0.142</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.6859</v>
+        <v>-0.6356000000000001</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9278</v>
+        <v>-2.3195</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-3.4793</v>
       </c>
       <c r="R14" t="n">
-        <v>0.9278</v>
+        <v>1.1598</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5693</v>
+        <v>1.3761</v>
       </c>
       <c r="T14" t="n">
-        <v>1.1325</v>
+        <v>1.4473</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5632</v>
+        <v>-0.0712</v>
       </c>
       <c r="V14" t="n">
-        <v>0.5361</v>
+        <v>2.8223</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5361</v>
+        <v>2.8223</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.2342</v>
+        <v>2.2735</v>
       </c>
       <c r="E15" t="n">
-        <v>1.5715</v>
+        <v>1.4536</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6627</v>
+        <v>0.8199</v>
       </c>
       <c r="G15" t="n">
         <v>0.4374</v>
@@ -1624,13 +1624,13 @@
         <v>0.9278</v>
       </c>
       <c r="S15" t="n">
-        <v>0.8689</v>
+        <v>0.9082</v>
       </c>
       <c r="T15" t="n">
-        <v>0.9911</v>
+        <v>0.8731</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1221</v>
+        <v>0.0351</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7877999999999999</v>
+        <v>0.8885999999999999</v>
       </c>
       <c r="E16" t="n">
         <v>1.1548</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.367</v>
+        <v>-0.2661</v>
       </c>
       <c r="G16" t="n">
         <v>0.0063</v>
@@ -1702,13 +1702,13 @@
         <v>0.9278</v>
       </c>
       <c r="S16" t="n">
-        <v>0.083</v>
+        <v>0.1838</v>
       </c>
       <c r="T16" t="n">
         <v>0.0395</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0435</v>
+        <v>0.1443</v>
       </c>
       <c r="V16" t="n">
         <v>0.9304</v>
@@ -1735,10 +1735,10 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1646</v>
+        <v>-0.0713</v>
       </c>
       <c r="E17" t="n">
-        <v>1.2036</v>
+        <v>0.9677</v>
       </c>
       <c r="F17" t="n">
         <v>-1.039</v>
@@ -1780,10 +1780,10 @@
         <v>0.9278</v>
       </c>
       <c r="S17" t="n">
-        <v>0.8022</v>
+        <v>0.5663</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6097</v>
+        <v>0.3738</v>
       </c>
       <c r="U17" t="n">
         <v>0.1924</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>U. GARUBA</t>
+          <t>T. MALEDON</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.089</v>
+        <v>-0.1746</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8587</v>
+        <v>2.547</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.9477</v>
+        <v>-2.7216</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.7816</v>
+        <v>-0.0451</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.1392</v>
+        <v>-0.7477</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.6424</v>
+        <v>0.7026</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.2659</v>
+        <v>1.503</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.4131</v>
+        <v>0.168</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1472</v>
+        <v>1.3349</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.5157</v>
+        <v>-1.5481</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.7261</v>
+        <v>-0.9157</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.7896</v>
+        <v>-0.6323</v>
       </c>
       <c r="P18" t="n">
-        <v>0.6959</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R18" t="n">
         <v>0.6959</v>
       </c>
       <c r="S18" t="n">
-        <v>0.9968</v>
+        <v>0.1926</v>
       </c>
       <c r="T18" t="n">
-        <v>1.1246</v>
+        <v>-0.0824</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1278</v>
+        <v>0.275</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.2862</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>T. MALEDON</t>
+          <t>U. GARUBA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4955</v>
+        <v>-0.5107</v>
       </c>
       <c r="E19" t="n">
-        <v>1.9572</v>
+        <v>0.2689</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.4527</v>
+        <v>-0.7796999999999999</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0451</v>
+        <v>-1.7816</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.7477</v>
+        <v>-1.1392</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7026</v>
+        <v>-0.6424</v>
       </c>
       <c r="J19" t="n">
-        <v>1.503</v>
+        <v>-0.2659</v>
       </c>
       <c r="K19" t="n">
-        <v>0.168</v>
+        <v>-0.4131</v>
       </c>
       <c r="L19" t="n">
-        <v>1.3349</v>
+        <v>0.1472</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.5481</v>
+        <v>-1.5157</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.9157</v>
+        <v>-0.7261</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.6323</v>
+        <v>-0.7896</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.4639</v>
+        <v>0.6959</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0.6959</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1283</v>
+        <v>0.575</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6721</v>
+        <v>0.5348000000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5439000000000001</v>
+        <v>0.0402</v>
       </c>
       <c r="V19" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>2.2862</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.1444</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.113</v>
+        <v>-0.7763</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.355</v>
+        <v>-0.1191</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.7581</v>
+        <v>-0.6573</v>
       </c>
       <c r="G20" t="n">
         <v>-0.4097</v>
@@ -2014,13 +2014,13 @@
         <v>0.4639</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0075</v>
+        <v>0.3293</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3383</v>
+        <v>0.5742</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3457</v>
+        <v>-0.2449</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.4057</v>
+        <v>-1.3048</v>
       </c>
       <c r="E21" t="n">
         <v>-1.0322</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.3734</v>
+        <v>-0.2726</v>
       </c>
       <c r="G21" t="n">
         <v>-1.4808</v>
@@ -2092,13 +2092,13 @@
         <v>0.4639</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3888</v>
+        <v>-0.288</v>
       </c>
       <c r="T21" t="n">
         <v>-0.3734</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0154</v>
+        <v>0.0854</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.037</v>
+        <v>-3.4479</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.991</v>
+        <v>-2.6935</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.046</v>
+        <v>-0.7543</v>
       </c>
       <c r="G22" t="n">
         <v>-3.6524</v>
@@ -2170,13 +2170,13 @@
         <v>1.1598</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.3847</v>
+        <v>0.2045</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8804</v>
+        <v>0.4171</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5043</v>
+        <v>-0.2126</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.5601</v>
+        <v>-6.4414</v>
       </c>
       <c r="E23" t="n">
-        <v>-6.9098</v>
+        <v>-5.6124</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.6502</v>
+        <v>-0.829</v>
       </c>
       <c r="G23" t="n">
         <v>-3.5051</v>
@@ -2248,13 +2248,13 @@
         <v>0.9278</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6607</v>
+        <v>0.458</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8057</v>
+        <v>0.4918</v>
       </c>
       <c r="U23" t="n">
-        <v>0.145</v>
+        <v>-0.0338</v>
       </c>
       <c r="V23" t="n">
         <v>-2.0026</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.2525</v>
+        <v>-2.4661</v>
       </c>
       <c r="E24" t="n">
-        <v>2.936000000000003</v>
+        <v>2.936000000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>-6.188400000000001</v>
+        <v>-5.4022</v>
       </c>
       <c r="G24" t="n">
         <v>-8.865500000000001</v>
@@ -2296,7 +2296,7 @@
         <v>-2.5746</v>
       </c>
       <c r="I24" t="n">
-        <v>-6.2907</v>
+        <v>-6.290699999999999</v>
       </c>
       <c r="J24" t="n">
         <v>1.181100000000002</v>
@@ -2311,7 +2311,7 @@
         <v>-10.0464</v>
       </c>
       <c r="N24" t="n">
-        <v>-2.920299999999999</v>
+        <v>-2.9203</v>
       </c>
       <c r="O24" t="n">
         <v>-7.126000000000001</v>
@@ -2326,13 +2326,13 @@
         <v>9.2782</v>
       </c>
       <c r="S24" t="n">
-        <v>4.3445</v>
+        <v>5.1309</v>
       </c>
       <c r="T24" t="n">
-        <v>5.1924</v>
+        <v>5.192399999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.8476999999999999</v>
+        <v>-0.06159999999999996</v>
       </c>
       <c r="V24" t="n">
         <v>2.427999999999999</v>
